--- a/out/LSTM-S4_repeat_3_000006.xlsx
+++ b/out/LSTM-S4_repeat_3_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003182443485300755</v>
+        <v>-5.113152705365792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4096052665998548</v>
+        <v>0.06581025827228758</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8199857033956912</v>
+        <v>0.1317450612097988</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09459469215750202</v>
+        <v>-0.01519829364927153</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3146923300938229</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3146923300938229</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3143502143535067</v>
+        <v>0.05049346794002224</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.051053543390544</v>
+        <v>0.2069603280649097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.418550194400052</v>
+        <v>0.4648262304554276</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2011072526204894</v>
+        <v>0.03959946472118359</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.768177349298667</v>
+        <v>0.3367629381030302</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3522584255924034</v>
+        <v>0.0693624355333953</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.271685529091668</v>
+        <v>0.4359076316691118</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1929092944863585</v>
+        <v>0.0379851555764479</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.304942543954438</v>
+        <v>0.4424561980214322</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.07967434801635837</v>
+        <v>0.01568861925315071</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.271179633400608</v>
+        <v>0.4358079836439788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.09926789085658703</v>
+        <v>0.0195461828627473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.390054046523393</v>
+        <v>0.4592153450370701</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05977150237155</v>
+        <v>0.01176817925537965</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.410262979452553</v>
+        <v>0.463193604961955</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04544330808900381</v>
+        <v>0.008945698889074837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.441351370475153</v>
+        <v>0.4693134159177437</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02009969343033049</v>
+        <v>0.003953926535315225</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.436067369092941</v>
+        <v>0.4682690490630101</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01594798971882997</v>
+        <v>0.003137675919314173</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.447858947345951</v>
+        <v>0.470587744349756</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.007907182072833864</v>
+        <v>0.001553422204039044</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.447712734533092</v>
+        <v>0.4705549303812415</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004594446378840305</v>
+        <v>0.0008997614318907874</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.448993177200602</v>
+        <v>0.470803118930717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002296177789792967</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.448985312078912</v>
+        <v>0.470797553875112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001130486024140772</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.448951533796679</v>
+        <v>0.4707868779063155</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0006558552500247418</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.449129284800089</v>
+        <v>0.4708178743160781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002159650412832189</v>
+        <v>3.740743216546624e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.44890481856548</v>
+        <v>0.4707696475226011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001050437662162811</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.448901050061624</v>
+        <v>0.470764896024337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.615490325271265e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.448906005702555</v>
+        <v>0.4707618871525233</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.344216536355913e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.448899067332668</v>
+        <v>0.4707565006683657</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.245520447377725e-05</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.448901061282462</v>
+        <v>0.4707531160499149</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.448893726888318</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.44889024166801</v>
+        <v>0.4707478291546989</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.448885694355825</v>
+        <v>0.4707480574757336</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.448885784300475</v>
+        <v>0.4707481474203835</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.44888492636689</v>
+        <v>0.4707472894867987</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.448885154687925</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.448884359023713</v>
+        <v>0.4707467221436217</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.448884421293086</v>
+        <v>0.4707467844129947</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.448884448968363</v>
+        <v>0.4707468120882716</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.448884601182386</v>
+        <v>0.4707469643022949</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.448884255241425</v>
+        <v>0.4707466183613331</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.448884331348436</v>
+        <v>0.4707466944683448</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.448884497400098</v>
+        <v>0.4707468605200064</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.448884857178697</v>
+        <v>0.4707472202986064</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.448884877935155</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.448884981717443</v>
+        <v>0.4707473448373526</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.448885210038478</v>
+        <v>0.4707475731583873</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.448885085499732</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.44888511317501</v>
+        <v>0.470747476294918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.448885168525563</v>
+        <v>0.470747531645472</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.448885431440694</v>
+        <v>0.4707477945606026</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.448885348414863</v>
+        <v>0.4707477115347719</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.448885140850286</v>
+        <v>0.470747503970195</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.448885154687925</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.448885293064309</v>
+        <v>0.4707476561842181</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.448885009392721</v>
+        <v>0.4707473725126295</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.44888483642224</v>
+        <v>0.4707471995421487</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.448884732639951</v>
+        <v>0.4707470957598602</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.448884877935155</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.448885120093828</v>
+        <v>0.4707474832137374</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.448884947123348</v>
+        <v>0.4707473102432564</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.448884649614121</v>
+        <v>0.4707470127340295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.448884635776482</v>
+        <v>0.4707469988963909</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.448884269079063</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.448884269079063</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.44888420680969</v>
+        <v>0.4707465699295986</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.448884103027401</v>
+        <v>0.4707464661473101</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.44888393005692</v>
+        <v>0.4707462931768294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.448883978488655</v>
+        <v>0.4707463416085639</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.448883618710055</v>
+        <v>0.4707459818299639</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.44888357719714</v>
+        <v>0.4707459403170485</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.448883632547693</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.448883687898248</v>
+        <v>0.4707460510181561</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.448883729411163</v>
+        <v>0.4707460925310715</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.448883459577213</v>
+        <v>0.4707458226971214</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.448883514927766</v>
+        <v>0.4707458780476754</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.44888366022297</v>
+        <v>0.4707460233428792</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.448883625628874</v>
+        <v>0.470745988748783</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.448883611791236</v>
+        <v>0.4707459749111444</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.448883701735886</v>
+        <v>0.4707460648557947</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.44888402000157</v>
+        <v>0.4707463831214793</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.44888384011227</v>
+        <v>0.4707462032321791</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.448883881625186</v>
+        <v>0.4707462447450946</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.448883694817066</v>
+        <v>0.4707460579369753</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.448883764005259</v>
+        <v>0.4707461271251678</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.448883563359501</v>
+        <v>0.4707459264794099</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.448883604872417</v>
+        <v>0.4707459679923253</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.448883632547693</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_3_000006.xlsx
+++ b/out/LSTM-S4_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.901262215535431</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003182443485300755</v>
+        <v>-0.0002686754126119195</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4096052665998548</v>
+        <v>0.3458061848389488</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8199857033956912</v>
+        <v>0.6922668013220471</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09459469215750202</v>
+        <v>-0.07986086183055981</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3146923300938229</v>
+        <v>0.2656766475957772</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3146923300938229</v>
+        <v>0.2656766475957772</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3143502143535067</v>
+        <v>0.2653933464207696</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.051053543390544</v>
+        <v>0.8703623167069233</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.418550194400052</v>
+        <v>2.007851399819665</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2011072526204894</v>
+        <v>0.166534022360738</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.768177349298667</v>
+        <v>1.469286803720096</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3522584255924034</v>
+        <v>0.2917001339333443</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.271685529091668</v>
+        <v>1.886234994269996</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1929092944863585</v>
+        <v>0.1597456084835373</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.304942543954438</v>
+        <v>1.913774690926221</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.07967434801635837</v>
+        <v>0.06597745953624483</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.7627717100636433</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.271179633400608</v>
+        <v>1.885816061298019</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.09926789085658703</v>
+        <v>0.08220225277805732</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.390054046523393</v>
+        <v>1.984254181339068</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05977150237155</v>
+        <v>0.04949637443189991</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.7627717100636433</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.410262979452553</v>
+        <v>2.000988895043862</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04544330808900381</v>
+        <v>0.03763055059207997</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.441351370475153</v>
+        <v>2.026732471389823</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02009969343033049</v>
+        <v>0.01664409045736639</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.436067369092941</v>
+        <v>2.022356912265639</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01594798971882997</v>
+        <v>0.01320634547782315</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.447858947345951</v>
+        <v>2.032120384105105</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.007907182072833864</v>
+        <v>0.006546376809595919</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.447712734533092</v>
+        <v>2.03199845828883</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004594446378840305</v>
+        <v>0.003803143776029069</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.448993177200602</v>
+        <v>2.033057819759406</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002296177789792967</v>
+        <v>0.001900526488387349</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.448985312078912</v>
+        <v>2.033050447250295</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001130486024140772</v>
+        <v>0.0009350099490988166</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.448951533796679</v>
+        <v>2.033021617248552</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0006558552500247418</v>
+        <v>0.0005423750555760488</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.449129284800089</v>
+        <v>2.033167986766528</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002159650412832189</v>
+        <v>0.0001780215493456964</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.44890481856548</v>
+        <v>2.032981206653014</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001050437662162811</v>
+        <v>8.707743703811276e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.448901050061624</v>
+        <v>2.032977225510131</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.615490325271265e-05</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.448906005702555</v>
+        <v>2.032980390668633</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.344216536355913e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.448899067332668</v>
+        <v>2.032973762675892</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.245520447377725e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.448901061282462</v>
+        <v>2.032974680912037</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.448893726888318</v>
+        <v>2.032967678621217</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.44889024166801</v>
+        <v>2.032963816546121</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.448885694355825</v>
+        <v>2.032959269233936</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.448885784300475</v>
+        <v>2.032959359178586</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.44888492636689</v>
+        <v>2.032958501245</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.448885154687925</v>
+        <v>2.032958729566035</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.448884359023713</v>
+        <v>2.032957933901824</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.448884421293086</v>
+        <v>2.032957996171196</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.448884448968363</v>
+        <v>2.032958023846474</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.448884601182386</v>
+        <v>2.032958176060496</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.448884255241425</v>
+        <v>2.032957830119535</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.448884331348436</v>
+        <v>2.032957906226546</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.448884497400098</v>
+        <v>2.032958072278208</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.448884857178697</v>
+        <v>2.032958432056808</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.448884877935155</v>
+        <v>2.032958452813266</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.448884981717443</v>
+        <v>2.032958556595554</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.448885210038478</v>
+        <v>2.032958784916589</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.448885085499732</v>
+        <v>2.032958660377843</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.44888511317501</v>
+        <v>2.03295868805312</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.448885168525563</v>
+        <v>2.032958743403674</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.448885431440694</v>
+        <v>2.032959006318805</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.448885348414863</v>
+        <v>2.032958923292973</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.448885140850286</v>
+        <v>2.032958715728396</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.448885154687925</v>
+        <v>2.032958729566035</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.448885293064309</v>
+        <v>2.03295886794242</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.448885009392721</v>
+        <v>2.032958584270831</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.44888483642224</v>
+        <v>2.03295841130035</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.448884732639951</v>
+        <v>2.032958307518062</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.448884877935155</v>
+        <v>2.032958452813266</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.448885120093828</v>
+        <v>2.032958694971939</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.448884947123348</v>
+        <v>2.032958522001458</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.448884649614121</v>
+        <v>2.032958224492231</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.448884635776482</v>
+        <v>2.032958210654593</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.448884269079063</v>
+        <v>2.032957843957173</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.448884269079063</v>
+        <v>2.032957843957173</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.44888420680969</v>
+        <v>2.0329577816878</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.448884103027401</v>
+        <v>2.032957677905511</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.44888393005692</v>
+        <v>2.032957504935031</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.448883978488655</v>
+        <v>2.032957553366765</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.448883618710055</v>
+        <v>2.032957193588166</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.44888357719714</v>
+        <v>2.03295715207525</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.448883632547693</v>
+        <v>2.032957207425804</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.448883687898248</v>
+        <v>2.032957262776358</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.448883729411163</v>
+        <v>2.032957304289273</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.448883459577213</v>
+        <v>2.032957034455323</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.448883514927766</v>
+        <v>2.032957089805877</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.44888366022297</v>
+        <v>2.032957235101081</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.448883625628874</v>
+        <v>2.032957200506985</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.448883611791236</v>
+        <v>2.032957186669346</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.448883701735886</v>
+        <v>2.032957276613996</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.44888402000157</v>
+        <v>2.032957594879681</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.44888384011227</v>
+        <v>2.032957414990381</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.448883881625186</v>
+        <v>2.032957456503296</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.448883694817066</v>
+        <v>2.032957269695177</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.448883764005259</v>
+        <v>2.032957338883369</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.448883563359501</v>
+        <v>2.032957138237612</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.448883604872417</v>
+        <v>2.032957179750527</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.448883632547693</v>
+        <v>2.032957207425804</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_3_000006.xlsx
+++ b/out/LSTM-S4_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.006599996238946915</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.004271950572729111</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002941016107797623</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.002003490924835205</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001624718308448792</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001072414219379425</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.000997595489025116</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0006208382546901703</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0002665407955646515</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0003637745976448059</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0006026625633239746</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0006375536322593689</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0002002716064453125</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-4.07882034778595e-05</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0001320168375968933</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0002739205956459045</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-5.784258246421814e-05</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.256106472331563</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0003652051091194153</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0009304210543632507</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.669436947795724</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.001021280884742737</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.669436947795724</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0008080191910266876</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.669436947795724</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0005047619342803955</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.669436947795724</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0004169940948486328</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.669436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0009315758943557739</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.669436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.00101051852107048</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.669436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001497026532888412</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.669436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.002824589610099792</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.669436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.00296180322766304</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.469436947795724</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.002570308744907379</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.469436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002144567668437958</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.469436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001571886241436005</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.469436947795724</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.001020405441522598</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001016877591609955</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002021882683038712</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002124663442373276</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001978609710931778</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.469436947795724</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001926325261592865</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.469436947795724</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001383241266012192</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.469436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.001236423850059509</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.469436947795724</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001426041126251221</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.469436947795724</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001909863203763962</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.002429652959108353</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.469436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.00339672714471817</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.469436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002686754126119195</v>
+        <v>-0.0001987187176558655</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3458061848389488</v>
+        <v>0.2557662586041952</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.00347021222114563</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.469436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6922668013220471</v>
+        <v>0.5120169718848381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07986086183055981</v>
+        <v>-0.05906703913986523</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.001927308738231659</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.469436947795724</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2656766475957772</v>
+        <v>0.1965005007466741</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.001011330634355545</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2656766475957772</v>
+        <v>0.1965005007466741</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0006876736879348755</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2653933464207696</v>
+        <v>0.1964534501824835</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8703623167069233</v>
+        <v>0.1445493465182455</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>6.169825792312622e-05</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.007851399819665</v>
+        <v>0.4858402999376156</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.166534022360738</v>
+        <v>0.02765788872429484</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0002425722777843475</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.469286803720096</v>
+        <v>0.3963955887397581</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2917001339333443</v>
+        <v>0.0484454151219277</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0003648586571216583</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.886234994269996</v>
+        <v>0.4656423992905426</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1597456084835373</v>
+        <v>0.02653047227828255</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.0002278834581375122</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7627717100636435</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.913774690926221</v>
+        <v>0.4702162132174163</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06597745953624483</v>
+        <v>0.01095684401023306</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0003360137343406677</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7627717100636433</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.885816061298019</v>
+        <v>0.4655719639539772</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.08220225277805732</v>
+        <v>0.01365185791096979</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.0005139485001564026</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.984254181339068</v>
+        <v>0.4819203071221248</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04949637443189991</v>
+        <v>0.008217556647750602</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0001205690205097198</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7627717100636433</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.000988895043862</v>
+        <v>0.4846973332921146</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03763055059207997</v>
+        <v>0.006247194326371021</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0003616102039813995</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.026732471389823</v>
+        <v>0.4889701733622577</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01664409045736639</v>
+        <v>0.002760368194078078</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.001622878015041351</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.022356912265639</v>
+        <v>0.488239305371542</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01320634547782315</v>
+        <v>0.002189324277530763</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.003046106547117233</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.032120384105105</v>
+        <v>0.4898567892394946</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006546376809595919</v>
+        <v>0.001083143914537696</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.00109437108039856</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.03199845828883</v>
+        <v>0.48983236857127</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003803143776029069</v>
+        <v>0.0006262965618016104</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0004515163600444794</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.033057819759406</v>
+        <v>0.4900041540600406</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001900526488387349</v>
+        <v>0.00031210288127362</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.002108167856931686</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.033050447250295</v>
+        <v>0.4899987592455473</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009350099490988166</v>
+        <v>0.0001502310007686119</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.003683429211378098</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.033021617248552</v>
+        <v>0.4899897951345918</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005423750555760488</v>
+        <v>8.511662500337389e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.004824452102184296</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.033167986766528</v>
+        <v>0.4900101792868548</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001780215493456964</v>
+        <v>2.624758159560671e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.006645884364843369</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.032981206653014</v>
+        <v>0.4899741436577181</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.707743703811276e-05</v>
+        <v>1.07205380308973e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.007559821009635925</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.032977225510131</v>
+        <v>0.4899693176089332</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.392392260217012e-05</v>
+        <v>2.338588390325519e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.008079130202531815</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.032980390668633</v>
+        <v>0.4899657129316025</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.008002683520317078</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.032973762675892</v>
+        <v>0.4899604025544566</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.007436234503984451</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.032974680912037</v>
+        <v>0.4899564782681055</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.007107332348823547</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.032967678621217</v>
+        <v>0.4899561461647823</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006650868803262711</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.032963816546121</v>
+        <v>0.4899565266998401</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.007374435663223267</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.032959269233936</v>
+        <v>0.4899567550208748</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.008318983018398285</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.032959359178586</v>
+        <v>0.4899568449655247</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.009138990193605423</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.032958501245</v>
+        <v>0.4899559870319399</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.009399693459272385</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.032958729566035</v>
+        <v>0.4899562153529746</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.009474143385887146</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.032957933901824</v>
+        <v>0.4899554196887629</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.009649675339460373</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.032957996171196</v>
+        <v>0.489955481958136</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.00917622447013855</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.032958023846474</v>
+        <v>0.4899555096334128</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.008402347564697266</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.032958176060496</v>
+        <v>0.4899556618474361</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.008302509784698486</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.032957830119535</v>
+        <v>0.4899553159064743</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.008024081587791443</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.032957906226546</v>
+        <v>0.489955392013486</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.008075002580881119</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.032958072278208</v>
+        <v>0.4899555580651476</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.00726420059800148</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.032958432056808</v>
+        <v>0.4899559178437476</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.006905306130647659</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.032958452813266</v>
+        <v>0.4899559386002054</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.006655767560005188</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.032958556595554</v>
+        <v>0.4899560423824939</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.007234353572130203</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.032958784916589</v>
+        <v>0.4899562707035285</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.007999099791049957</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.032958660377843</v>
+        <v>0.4899561461647823</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.008596386760473251</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.03295868805312</v>
+        <v>0.4899561738400592</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.008112974464893341</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.032958743403674</v>
+        <v>0.4899562291906132</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.008294221013784409</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.032959006318805</v>
+        <v>0.4899564921057438</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.008223459124565125</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.032958923292973</v>
+        <v>0.4899564090799131</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.008290596306324005</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.032958715728396</v>
+        <v>0.4899562015153363</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.008260581642389297</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.032958729566035</v>
+        <v>0.4899562153529746</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.008024547249078751</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.03295886794242</v>
+        <v>0.4899563537293594</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.008240316063165665</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.032958584270831</v>
+        <v>0.4899560700577707</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.008499648422002792</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.03295841130035</v>
+        <v>0.4899558970872899</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.007943332195281982</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.032958307518062</v>
+        <v>0.4899557933050014</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.007528021931648254</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.032958452813266</v>
+        <v>0.4899559386002054</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.007427029311656952</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.032958694971939</v>
+        <v>0.4899561807588786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.007573023438453674</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.032958522001458</v>
+        <v>0.4899560077883976</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.007887706160545349</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.032958224492231</v>
+        <v>0.4899557102791707</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.008148770779371262</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.032958210654593</v>
+        <v>0.4899556964415321</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.008267618715763092</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.032957843957173</v>
+        <v>0.4899553297441129</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.008021548390388489</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.032957843957173</v>
+        <v>0.4899553297441129</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.007591702044010162</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.0329577816878</v>
+        <v>0.4899552674747398</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.007784917950630188</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.032957677905511</v>
+        <v>0.4899551636924513</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00786924734711647</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.032957504935031</v>
+        <v>0.4899549907219706</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.007616244256496429</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.032957553366765</v>
+        <v>0.4899550391537051</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.007333490997552872</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.032957193588166</v>
+        <v>0.4899546793751051</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.006965074688196182</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.03295715207525</v>
+        <v>0.4899546378621897</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.006233640015125275</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.032957207425804</v>
+        <v>0.4899546932127434</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.005913607776165009</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.032957262776358</v>
+        <v>0.4899547485632973</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.005787264555692673</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.032957304289273</v>
+        <v>0.4899547900762127</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.005599252879619598</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.032957034455323</v>
+        <v>0.4899545202422627</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.005208127200603485</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.032957089805877</v>
+        <v>0.4899545755928166</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.004943430423736572</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.032957235101081</v>
+        <v>0.4899547208880204</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.004652798175811768</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.032957200506985</v>
+        <v>0.4899546862939242</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.004555903375148773</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.032957186669346</v>
+        <v>0.4899546724562857</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003889944404363632</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.032957276613996</v>
+        <v>0.4899547624009359</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002586759626865387</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.032957594879681</v>
+        <v>0.4899550806666205</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003006603568792343</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.032957414990381</v>
+        <v>0.4899549007773204</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003682289272546768</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.032957456503296</v>
+        <v>0.4899549422902358</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.004121165722608566</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.032957269695177</v>
+        <v>0.4899547554821165</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.004608567804098129</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.032957338883369</v>
+        <v>0.489954824670309</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.004639435559511185</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.032957138237612</v>
+        <v>0.4899546240245511</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004594072699546814</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.3000000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.032957179750527</v>
+        <v>0.4899546655374665</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.004236292093992233</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4400000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.032957207425804</v>
+        <v>0.4899546932127434</v>
       </c>
     </row>
   </sheetData>
